--- a/output/roomself_excel/5890.xlsx
+++ b/output/roomself_excel/5890.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>213112</v>
+        <v>39600</v>
       </c>
       <c r="D2" t="n">
-        <v>4080</v>
+        <v>1616</v>
       </c>
       <c r="E2" t="n">
-        <v>580</v>
+        <v>174</v>
       </c>
       <c r="F2" t="n">
-        <v>470</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
@@ -488,19 +488,63 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Living Room</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>90102</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2492</v>
+      </c>
+      <c r="E3" t="n">
+        <v>405</v>
+      </c>
+      <c r="F3" t="n">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C4" t="n">
+        <v>83410</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2428</v>
+      </c>
+      <c r="E4" t="n">
+        <v>409</v>
+      </c>
+      <c r="F4" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
         <v>28458</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D5" t="n">
         <v>1480</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E5" t="n">
         <v>157</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F5" t="n">
         <v>107</v>
       </c>
     </row>

--- a/output/roomself_excel/5890.xlsx
+++ b/output/roomself_excel/5890.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,11 +510,38 @@
       <c r="D2" t="n">
         <v>1616</v>
       </c>
-      <c r="E2" t="n">
-        <v>174</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>42</v>
+        <v>159</v>
+      </c>
+      <c r="G2" t="n">
+        <v>14</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>28</v>
+      </c>
+      <c r="J2" t="n">
+        <v>27</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>202</v>
+      </c>
+      <c r="M2" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -497,12 +559,31 @@
       <c r="D3" t="n">
         <v>2492</v>
       </c>
-      <c r="E3" t="n">
-        <v>405</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>245</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="G3" t="n">
+        <v>14</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>205</v>
+      </c>
+      <c r="J3" t="n">
+        <v>13</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +600,31 @@
       <c r="D4" t="n">
         <v>2428</v>
       </c>
-      <c r="E4" t="n">
-        <v>409</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>225</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="G4" t="n">
+        <v>13</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>396</v>
+      </c>
+      <c r="J4" t="n">
+        <v>14</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,11 +641,38 @@
       <c r="D5" t="n">
         <v>1480</v>
       </c>
-      <c r="E5" t="n">
-        <v>157</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>107</v>
+        <v>105</v>
+      </c>
+      <c r="G5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>79</v>
+      </c>
+      <c r="J5" t="n">
+        <v>38</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>131</v>
+      </c>
+      <c r="M5" t="n">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
